--- a/astro-site/public/dl/ghost-kitchen-checklist-templates/BONUS-02-ghost-kitchen-delivery-calendar.xlsx
+++ b/astro-site/public/dl/ghost-kitchen-checklist-templates/BONUS-02-ghost-kitchen-delivery-calendar.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Summer kicks off: extra staff and summer stock, review prep times for the peak; decide the holiday hours and post them in each app</t>
+          <t>Summer kicks off: decide the holiday hours and post them in each app, set up the summer menu and plan staffing for the slower summer weeks</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Summer peak season</t>
+          <t>Summer slowdown (warm weather, vacations, school break)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Extra staff, extended hours and a summer menu by brand</t>
+          <t>Delivery usually dips: trim prep and shifts, keep the hours steady, push lunch combos and hot-weather items (bowls, salads, cold drinks) and plan the fall menu; near beaches, tourist areas or summer events it can run the other way</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
